--- a/casestudy/esg_reporting/companies.xlsx
+++ b/casestudy/esg_reporting/companies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nb\ESG_case\FinancialDataAnalytics\casestudy\esg_reporting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86EDD2A0-0EAC-4A22-BC5B-720CDD482708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CD6CC5-9140-40FA-9596-0C30AB407A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{0602BCDD-BCC7-4964-853A-E57B262E4FB2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0602BCDD-BCC7-4964-853A-E57B262E4FB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Student</t>
   </si>
@@ -83,9 +83,6 @@
     <t>JPMorgan Chase</t>
   </si>
   <si>
-    <t>Deutsche Bank</t>
-  </si>
-  <si>
     <t>Pfizer</t>
   </si>
   <si>
@@ -126,6 +123,27 @@
   </si>
   <si>
     <t>AXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jonahein </t>
+  </si>
+  <si>
+    <t>jannkrn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sonjaschnik </t>
+  </si>
+  <si>
+    <t xml:space="preserve">zahrasaeidi02 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bewater-yo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MergenToprak </t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
   </si>
 </sst>
 </file>
@@ -525,6 +543,9 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -539,6 +560,9 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -553,59 +577,71 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
       <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
